--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486910_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486910_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5819</v>
+        <v>12.9978</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6402</v>
+        <v>12.0857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9417</v>
+        <v>0.9121</v>
       </c>
       <c r="G2" t="n">
         <v>6.2486</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3251</v>
+        <v>0.741</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0854</v>
+        <v>0.3602</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4104</v>
+        <v>0.3808</v>
       </c>
       <c r="V2" t="n">
         <v>4.3654</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.6341</v>
+        <v>8.476100000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7128</v>
+        <v>4.7326</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9213</v>
+        <v>3.7435</v>
       </c>
       <c r="G3" t="n">
         <v>4.0914</v>
@@ -688,13 +688,13 @@
         <v>2.8748</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7295</v>
+        <v>0.5715</v>
       </c>
       <c r="T3" t="n">
-        <v>1.317</v>
+        <v>0.3369</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4125</v>
+        <v>0.2346</v>
       </c>
       <c r="V3" t="n">
         <v>0.9384</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0764</v>
+        <v>5.881</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7544</v>
+        <v>5.6184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3219</v>
+        <v>0.2626</v>
       </c>
       <c r="G4" t="n">
         <v>5.2298</v>
@@ -766,13 +766,13 @@
         <v>2.4641</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2603</v>
+        <v>0.5444</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.651</v>
+        <v>0.213</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3907</v>
+        <v>0.3314</v>
       </c>
       <c r="V4" t="n">
         <v>-2.3573</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3474</v>
+        <v>3.643</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4377</v>
+        <v>2.674</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9097</v>
+        <v>0.969</v>
       </c>
       <c r="G5" t="n">
         <v>2.759</v>
@@ -844,13 +844,13 @@
         <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.3583</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2171</v>
+        <v>0.0192</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2798</v>
+        <v>0.3391</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5277</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1707</v>
+        <v>1.398</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1116</v>
+        <v>1.1314</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0591</v>
+        <v>0.2666</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6765</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6767</v>
+        <v>-0.096</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3752</v>
+        <v>0.395</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6985</v>
+        <v>-0.491</v>
       </c>
       <c r="V6" t="n">
         <v>0.9384</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9644</v>
+        <v>1.0428</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1463</v>
+        <v>0.3768</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1107</v>
+        <v>0.666</v>
       </c>
       <c r="G7" t="n">
         <v>0.5168</v>
@@ -1000,13 +1000,13 @@
         <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.614</v>
+        <v>-0.5356</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.899</v>
+        <v>-0.376</v>
       </c>
       <c r="U7" t="n">
-        <v>0.285</v>
+        <v>-0.1596</v>
       </c>
       <c r="V7" t="n">
         <v>0.2402</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8218</v>
+        <v>1.0136</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6371</v>
+        <v>1.5325</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8154</v>
+        <v>-0.5189</v>
       </c>
       <c r="G8" t="n">
         <v>1.6564</v>
@@ -1078,13 +1078,13 @@
         <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0113</v>
+        <v>-0.8194</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.283</v>
+        <v>-0.3876</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.4318</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8768</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3945</v>
+        <v>-0.0964</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0325</v>
+        <v>-0.8233</v>
       </c>
       <c r="F9" t="n">
-        <v>0.638</v>
+        <v>0.7269</v>
       </c>
       <c r="G9" t="n">
         <v>0.5806</v>
@@ -1156,13 +1156,13 @@
         <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3858</v>
+        <v>-1.0877</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7091</v>
+        <v>-0.4999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6767</v>
+        <v>-0.5878</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4157</v>
+        <v>-1.4297</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8518</v>
+        <v>-0.7472</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5639</v>
+        <v>-0.6825</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5456</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5129</v>
+        <v>-0.5269</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2558</v>
+        <v>-0.1512</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2571</v>
+        <v>-0.3757</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2602</v>
+        <v>-2.7414</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3072</v>
+        <v>-5.9662</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0469</v>
+        <v>3.2248</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1812</v>
@@ -1312,13 +1312,13 @@
         <v>3.0801</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.1763</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.2633</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.4396</v>
       </c>
       <c r="V11" t="n">
         <v>0.5893</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>29.5263</v>
+        <v>30.1848</v>
       </c>
       <c r="E12" t="n">
-        <v>19.956</v>
+        <v>20.6147</v>
       </c>
       <c r="F12" t="n">
-        <v>9.57</v>
+        <v>9.5701</v>
       </c>
       <c r="G12" t="n">
         <v>15.6793</v>
@@ -1390,10 +1390,10 @@
         <v>20.5342</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6854</v>
+        <v>-1.026699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4859</v>
+        <v>0.1729000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-1.1996</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7091</v>
+        <v>2.0885</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9519</v>
+        <v>3.6967</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2428</v>
+        <v>-1.6081</v>
       </c>
       <c r="G13" t="n">
         <v>-0.035</v>
@@ -1468,13 +1468,13 @@
         <v>0.616</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5387</v>
+        <v>0.9181</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9563</v>
+        <v>0.701</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4175</v>
+        <v>0.2171</v>
       </c>
       <c r="V13" t="n">
         <v>0.5893</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1236</v>
+        <v>1.0337</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2712</v>
+        <v>3.585</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1476</v>
+        <v>-2.5513</v>
       </c>
       <c r="G14" t="n">
         <v>3.2858</v>
@@ -1546,13 +1546,13 @@
         <v>0.616</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4393</v>
+        <v>0.4708</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1435</v>
+        <v>0.1703</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2958</v>
+        <v>0.3005</v>
       </c>
       <c r="V14" t="n">
         <v>1.1786</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.2452</v>
+        <v>-0.9548</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2967</v>
+        <v>0.3936</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9485</v>
+        <v>-1.3483</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4783</v>
+        <v>-0.2256</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1977</v>
+        <v>-0.4834</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.2579</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.2581</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6653</v>
+        <v>-0.347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1579</v>
+        <v>0.605</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3014</v>
+        <v>-0.4836</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4676</v>
+        <v>-0.1365</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8338</v>
+        <v>-0.3472</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.4374</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6786</v>
+        <v>0.2441</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3176</v>
+        <v>0.1355</v>
       </c>
       <c r="U15" t="n">
-        <v>1.361</v>
+        <v>0.1086</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3208</v>
+        <v>-1.8229</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.185</v>
+        <v>-0.708</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1358</v>
+        <v>-1.1149</v>
       </c>
       <c r="G16" t="n">
         <v>-3.172</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9477</v>
+        <v>0.4456</v>
       </c>
       <c r="T16" t="n">
-        <v>0.736</v>
+        <v>0.213</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2117</v>
+        <v>0.2326</v>
       </c>
       <c r="V16" t="n">
         <v>0.6982</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8753</v>
+        <v>-1.9009</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1295</v>
+        <v>-0.4013</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7459</v>
+        <v>-1.4996</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2256</v>
+        <v>-0.4783</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4834</v>
+        <v>0.1977</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2579</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2581</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.347</v>
+        <v>0.6653</v>
       </c>
       <c r="L17" t="n">
-        <v>0.605</v>
+        <v>0.1579</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4836</v>
+        <v>-1.3014</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1365</v>
+        <v>-0.4676</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3472</v>
+        <v>-0.8338</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6765</v>
+        <v>1.0229</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3875</v>
+        <v>0.213</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2889</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6545</v>
+        <v>-2.5952</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0264</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6281</v>
+        <v>-2.5688</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2709</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0263</v>
+        <v>0.0329</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V18" t="n">
         <v>-2.3573</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3028</v>
+        <v>-2.6874</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6481</v>
+        <v>-0.4389</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6547</v>
+        <v>-2.2485</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7655999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6358</v>
+        <v>-0.0203</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1822</v>
+        <v>0.027</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4536</v>
+        <v>-0.0474</v>
       </c>
       <c r="V19" t="n">
         <v>1.1786</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6606</v>
+        <v>-3.8626</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8428</v>
+        <v>-1.1146</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1822</v>
+        <v>-2.748</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3719</v>
+        <v>-2.4117</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.288</v>
+        <v>-2.2382</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.084</v>
+        <v>-0.1736</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6308</v>
+        <v>0.9312</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9859</v>
+        <v>-0.2394</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6449</v>
+        <v>1.1706</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7411</v>
+        <v>-3.3429</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.302</v>
+        <v>-1.9988</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4391</v>
+        <v>-1.3441</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.4908</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1068</v>
+        <v>-2.4641</v>
       </c>
       <c r="R20" t="n">
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0235</v>
+        <v>0.3972</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4144</v>
+        <v>0.4183</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6092</v>
+        <v>-0.0211</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2566</v>
+        <v>-3.9848</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4284</v>
+        <v>-5.3658</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8282</v>
+        <v>1.381</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4117</v>
+        <v>-2.3719</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2382</v>
+        <v>-1.288</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1736</v>
+        <v>-1.084</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9312</v>
+        <v>-1.6308</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2394</v>
+        <v>-0.9859</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1706</v>
+        <v>-0.6449</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3429</v>
+        <v>-0.7411</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9988</v>
+        <v>-0.302</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3441</v>
+        <v>-0.4391</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8481</v>
+        <v>-3.4908</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4641</v>
+        <v>-4.1068</v>
       </c>
       <c r="R21" t="n">
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0032</v>
+        <v>0.6993</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1045</v>
+        <v>-0.1087</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1013</v>
+        <v>0.8079</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3042</v>
+        <v>-5.8195</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0699</v>
+        <v>-4.5469</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2343</v>
+        <v>-1.2727</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1559</v>
@@ -2170,13 +2170,13 @@
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4788</v>
+        <v>0.0058</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7169</v>
+        <v>-0.1939</v>
       </c>
       <c r="U22" t="n">
-        <v>0.238</v>
+        <v>0.1996</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.7388</v>
+        <v>-6.9281</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1664</v>
+        <v>-4.6434</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5724</v>
+        <v>-2.2847</v>
       </c>
       <c r="G23" t="n">
         <v>-6.0786</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2495</v>
+        <v>-0.4388</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.3101</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4164</v>
+        <v>-0.1287</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-29.5261</v>
+        <v>-27.434</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.5701</v>
+        <v>-9.57</v>
       </c>
       <c r="F24" t="n">
-        <v>-19.9561</v>
+        <v>-17.8639</v>
       </c>
       <c r="G24" t="n">
         <v>-15.6797</v>
@@ -2299,7 +2299,7 @@
         <v>-8.590399999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>4.438300000000002</v>
+        <v>4.4383</v>
       </c>
       <c r="K24" t="n">
         <v>4.690999999999999</v>
@@ -2326,22 +2326,22 @@
         <v>5.1334</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6855</v>
+        <v>3.777599999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>1.199599999999999</v>
+        <v>1.1995</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4858999999999999</v>
+        <v>2.5779</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1314999999999995</v>
+        <v>-0.1314999999999997</v>
       </c>
       <c r="W24" t="n">
         <v>5.3263</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.4577</v>
+        <v>-5.457700000000001</v>
       </c>
     </row>
   </sheetData>
